--- a/02_DIA_inicio_2026_analisis_assets/rbd_9730_colegio-antu_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9730_colegio-antu_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01794B03-59F9-445A-BE23-BB4ED1CF22FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C6166F5-7192-49CB-B3EA-C2D20E5AE40A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C23A909-FA98-4FFF-BBEA-0352BF27F056}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F11C27E-5809-4F27-A3A7-C852B5554783}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{940EC3C3-78E7-46CB-8E26-94CE5ACE5BF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7426CC66-0966-4771-809A-8F37BF30E1BD}"/>
 </file>